--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12T13:48:53.140550</t>
+          <t>2026-09-13T14:44:37.823058</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:54</t>
+          <t>2026-09-13 14:44:37</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -533,35 +533,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Septiembre 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13T14:44:37.823058</t>
+          <t>2026-09-14T16:42:33.076932</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Septiembre 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40844.79</v>
+        <v>40873.77</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al 31 de Julio del 2026:</t>
+          <t>Al 31 de Agosto del 2026:</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3678639</v>
+        <v>3695148</v>
       </c>
       <c r="G2" t="n">
-        <v>2450687</v>
+        <v>2452426</v>
       </c>
       <c r="H2" t="n">
-        <v>5526134</v>
+        <v>5550933</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2043689</v>
+        <v>2052860</v>
       </c>
       <c r="L2" t="n">
-        <v>24524262</v>
+        <v>24634320</v>
       </c>
       <c r="M2" t="n">
-        <v>36786393</v>
+        <v>36951480</v>
       </c>
       <c r="N2" t="n">
         <v>553553</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:37</t>
+          <t>2026-09-14 16:42:34</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:42:33.076932</t>
+          <t>2026-09-15T15:20:53.108981</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:34</t>
+          <t>2026-09-15 15:20:53</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15T15:20:53.108981</t>
+          <t>2026-09-16T15:13:07.441420</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 15:20:53</t>
+          <t>2026-09-16 15:13:08</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16T15:13:07.441420</t>
+          <t>2026-09-17T15:22:33.057168</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:08</t>
+          <t>2026-09-17 15:22:33</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17T15:22:33.057168</t>
+          <t>2026-09-18T14:42:26.318041</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:33</t>
+          <t>2026-09-18 14:42:26</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:42:26.318041</t>
+          <t>2026-09-19T14:02:59.193167</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:26</t>
+          <t>2026-09-19 14:02:59</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T14:02:59.193167</t>
+          <t>2026-09-20T14:23:33.531262</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:02:59</t>
+          <t>2026-09-20 14:23:33</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20T14:23:33.531262</t>
+          <t>2026-09-21T16:42:54.453973</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:33</t>
+          <t>2026-09-21 16:42:54</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21T16:42:54.453973</t>
+          <t>2026-09-22T15:17:01.117540</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:54</t>
+          <t>2026-09-22 15:17:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22T15:17:01.117540</t>
+          <t>2026-09-23T15:14:21.052786</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:17:02</t>
+          <t>2026-09-23 15:14:21</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:14:21.052786</t>
+          <t>2026-09-24T15:36:24.443448</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:21</t>
+          <t>2026-09-24 15:36:24</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:36:24.443448</t>
+          <t>2026-09-25T15:41:12.496432</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:36:24</t>
+          <t>2026-09-25 15:41:12</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25T15:41:12.496432</t>
+          <t>2026-09-26T14:49:01.965795</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:41:12</t>
+          <t>2026-09-26 14:49:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26T14:49:01.965795</t>
+          <t>2026-09-27T15:27:52.977601</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:02</t>
+          <t>2026-09-27 15:27:53</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27T15:27:52.977601</t>
+          <t>2026-09-28T18:19:02.726269</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:53</t>
+          <t>2026-09-28 18:19:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28T18:19:02.726269</t>
+          <t>2026-09-29T16:42:00.068557</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:02</t>
+          <t>2026-09-29 16:42:00</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29T16:42:00.068557</t>
+          <t>2026-09-30T16:33:27.066094</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:42:00</t>
+          <t>2026-09-30 16:33:27</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30T16:33:27.066094</t>
+          <t>2026-10-01T17:11:57.521042</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:33:27</t>
+          <t>2026-10-01 17:11:57</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01T17:11:57.521042</t>
+          <t>2026-10-02T16:25:19.969266</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:11:57</t>
+          <t>2026-10-02 16:25:20</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02T16:25:19.969266</t>
+          <t>2026-10-03T14:59:43.432155</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:25:20</t>
+          <t>2026-10-03 14:59:44</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03T14:59:43.432155</t>
+          <t>2026-10-04T15:34:55.654592</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:59:44</t>
+          <t>2026-10-04 15:34:55</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04T15:34:55.654592</t>
+          <t>2026-10-05T19:26:59.973934</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04 15:34:55</t>
+          <t>2026-10-05 19:27:00</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05T19:26:59.973934</t>
+          <t>2026-10-06T17:00:08.035477</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:27:00</t>
+          <t>2026-10-06 17:00:08</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06T17:00:08.035477</t>
+          <t>2026-10-07T17:36:45.566780</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:00:08</t>
+          <t>2026-10-07 17:36:45</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:36:45.566780</t>
+          <t>2026-10-08T17:39:51.621445</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:36:45</t>
+          <t>2026-10-08 17:39:51</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08T17:39:51.621445</t>
+          <t>2026-10-09T17:15:15.502113</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -981,10 +981,26 @@
           <t>860.652</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>113,59</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1013,8 +1029,16 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>72.440</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>869.280</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -1067,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:39:51</t>
+          <t>2026-10-09 17:15:15</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09T17:15:15.502113</t>
+          <t>2026-10-10T16:02:07.646578</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 17:15:15</t>
+          <t>2026-10-10 16:02:07</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10T16:02:07.646578</t>
+          <t>2026-10-11T16:27:52.221568</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:02:07</t>
+          <t>2026-10-11 16:27:52</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11T16:27:52.221568</t>
+          <t>2026-10-12T20:03:28.846971</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:27:52</t>
+          <t>2026-10-12 20:03:28</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12T20:03:28.846971</t>
+          <t>2026-10-13T17:51:57.964897</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:03:28</t>
+          <t>2026-10-13 17:51:58</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -533,35 +533,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Septiembre 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13T17:51:57.964897</t>
+          <t>2026-10-14T15:38:20.665667</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Octubre 2026</t>
+          <t>Noviembre 2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40873.77</v>
+        <v>41057.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al 31 de Agosto del 2026:</t>
+          <t>Al 30 de Septiembre del 2026:</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3695148</v>
+        <v>3712287</v>
       </c>
       <c r="G2" t="n">
-        <v>2452426</v>
+        <v>2463432</v>
       </c>
       <c r="H2" t="n">
-        <v>5550933</v>
+        <v>5576680</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2052860</v>
+        <v>2062382</v>
       </c>
       <c r="L2" t="n">
-        <v>24634320</v>
+        <v>24748578</v>
       </c>
       <c r="M2" t="n">
-        <v>36951480</v>
+        <v>37122867</v>
       </c>
       <c r="N2" t="n">
         <v>553553</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:51:58</t>
+          <t>2026-10-14 15:38:22</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14T15:38:20.665667</t>
+          <t>2026-10-15T15:24:44.507141</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:38:22</t>
+          <t>2026-10-15 15:24:44</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15T15:24:44.507141</t>
+          <t>2026-10-16T15:04:34.542019</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:24:44</t>
+          <t>2026-10-16 15:04:34</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16T15:04:34.542019</t>
+          <t>2026-10-17T13:59:51.782250</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:04:34</t>
+          <t>2026-10-17 13:59:51</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:59:51.782250</t>
+          <t>2026-10-18T14:12:41.180672</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:59:51</t>
+          <t>2026-10-18 14:12:41</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18T14:12:41.180672</t>
+          <t>2026-10-19T17:16:14.415639</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 14:12:41</t>
+          <t>2026-10-19 17:16:14</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19T17:16:14.415639</t>
+          <t>2026-10-20T15:29:16.011275</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:16:14</t>
+          <t>2026-10-20 15:29:17</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20T15:29:16.011275</t>
+          <t>2026-10-21T15:45:11.260172</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 15:29:17</t>
+          <t>2026-10-21 15:45:11</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21T15:45:11.260172</t>
+          <t>2026-10-22T15:44:39.502790</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 15:45:11</t>
+          <t>2026-10-22 15:44:39</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22T15:44:39.502790</t>
+          <t>2026-10-23T15:32:46.721670</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22 15:44:39</t>
+          <t>2026-10-23 15:32:46</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23T15:32:46.721670</t>
+          <t>2026-10-24T14:10:17.571924</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:32:46</t>
+          <t>2026-10-24 14:10:17</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24T14:10:17.571924</t>
+          <t>2026-10-25T14:41:53.681378</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 14:10:17</t>
+          <t>2026-10-25 14:41:53</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25T14:41:53.681378</t>
+          <t>2026-10-26T17:04:01.517858</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 14:41:53</t>
+          <t>2026-10-26 17:04:01</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26T17:04:01.517858</t>
+          <t>2026-10-27T16:07:08.579937</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 17:04:01</t>
+          <t>2026-10-27 16:07:08</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27T16:07:08.579937</t>
+          <t>2026-10-28T16:54:08.252264</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 16:07:08</t>
+          <t>2026-10-28 16:54:08</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28T16:54:08.252264</t>
+          <t>2026-10-29T17:12:33.103944</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:54:08</t>
+          <t>2026-10-29 17:12:33</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:12:33.103944</t>
+          <t>2026-10-30T16:53:19.827126</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:12:33</t>
+          <t>2026-10-30 16:53:19</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30T16:53:19.827126</t>
+          <t>2026-10-31T15:55:13.113855</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:53:19</t>
+          <t>2026-10-31 15:55:13</t>
         </is>
       </c>
     </row>
